--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260806.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260806.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.88%</t>
+          <t>9.79%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.76%</t>
+          <t>8.81%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>5.93%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>5.24%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>186,198,000</t>
+          <t>186,546,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.69%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>27,028,000</t>
+          <t>27,148,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>5,030,000</t>
+          <t>5,037,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>430,925,000</t>
+          <t>436,925,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>358,289,964</t>
+          <t>359,789,964</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -902,29 +902,29 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>230,616,516</t>
+          <t>63,040,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -941,56 +941,56 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>82,618,000</t>
+          <t>82,730,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>63,040,000</t>
+          <t>26,144,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>26,144,000</t>
+          <t>230,616,516</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
@@ -1007,56 +1007,56 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>97,642,442</t>
+          <t>97,953,442</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>202,817,000</t>
+          <t>145,652,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>145,652,000</t>
+          <t>202,817,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>28,750,000</t>
+          <t>28,764,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>187,606,000</t>
+          <t>188,180,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,847,535,840</t>
+          <t>13,886,507,507</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,454,107,583</t>
+          <t>4,339,382,783</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-67,350,140</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
